--- a/marketing_forms/012_health_insights_opt_in_form--marketing_forms.xlsx
+++ b/marketing_forms/012_health_insights_opt_in_form--marketing_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>form_ids_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Form IDs</t>
+          <t>Form Ids 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
